--- a/output/laminas_comunales/comunal_m_movinterna_a_2022_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_m_movinterna_a_2022_metropolitana.xlsx
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2018_2022. Escala de colores estandarizada a nivel nacional para todo el periodo.</t>
+          <t>Periodo 2018_2022. Escala comunal recortada a percentiles 3-97. Sobre umbral: San Miguel (64,8); Independencia (67,4); Providencia (78,3); Calera de Tango (92,2); Santiago (79,6); Pirque (67,9); Vitacura (65,4); Estación Central (64,9); Ñuñoa (64,9); Tiltil (65,9).</t>
         </is>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_m_movinterna_a_2022_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_m_movinterna_a_2022_metropolitana.xlsx
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2018_2022. Escala comunal recortada a percentiles 3-97. Sobre umbral: San Miguel (64,8); Independencia (67,4); Providencia (78,3); Calera de Tango (92,2); Santiago (79,6); Pirque (67,9); Vitacura (65,4); Estación Central (64,9); Ñuñoa (64,9); Tiltil (65,9).</t>
+          <t>Periodo 2018_2022. Escala comunal recortada a percentiles 3-97. Sobre umbral: San Miguel (64,8); Independencia (67,4); Providencia (78,3); Calera de Tango (92,2); Santiago (79,6); Pirque (67,9); y 4 más.</t>
         </is>
       </c>
     </row>
